--- a/基础数据.xlsx
+++ b/基础数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11460"/>
+    <workbookView windowHeight="18460" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="唯普库" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="554">
   <si>
     <t>唯普库-服务中心
 库位清单</t>
@@ -70,6 +70,9 @@
 惠州服务中心
 广州花都空港（A区）
 惠州服务中心（A区）</t>
+  </si>
+  <si>
+    <t>问蚂蚁</t>
   </si>
   <si>
     <t>顺序</t>
@@ -3476,14 +3479,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
+    <col min="1" max="1" width="16.2307692307692" customWidth="1"/>
     <col min="3" max="3" width="30.4519230769231" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="23.6730769230769" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="396" customHeight="1" spans="1:5">
+    <row r="1" ht="396" customHeight="1" spans="1:6">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -3495,6 +3500,9 @@
         <v>2</v>
       </c>
       <c r="E1" s="14"/>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3519,10 +3527,10 @@
   <sheetData>
     <row r="1" ht="17" spans="1:2">
       <c r="A1" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3530,10 +3538,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3541,10 +3549,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3552,10 +3560,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3563,10 +3571,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3574,10 +3582,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3585,10 +3593,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3596,10 +3604,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3607,10 +3615,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3618,10 +3626,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3629,10 +3637,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3640,10 +3648,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3651,10 +3659,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3662,7 +3670,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3670,7 +3678,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3678,7 +3686,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3686,7 +3694,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3694,7 +3702,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3702,7 +3710,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3710,7 +3718,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3718,7 +3726,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3726,7 +3734,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3734,7 +3742,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3742,7 +3750,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3750,7 +3758,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3758,7 +3766,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3766,7 +3774,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3774,7 +3782,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3782,7 +3790,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3790,7 +3798,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3798,7 +3806,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3806,145 +3814,145 @@
         <v>31</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3958,1240 +3966,1243 @@
   <sheetPr/>
   <dimension ref="A3:A249"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="24.0384615384615" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -5211,10 +5222,10 @@
   <sheetData>
     <row r="1" s="8" customFormat="1" spans="1:2">
       <c r="A1" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" s="8" customFormat="1" spans="1:2">
@@ -5222,7 +5233,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" s="8" customFormat="1" spans="1:2">
@@ -5230,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" spans="1:2">
@@ -5238,7 +5249,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" s="8" customFormat="1" spans="1:2">
@@ -5246,7 +5257,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" s="8" customFormat="1" spans="1:2">
@@ -5254,7 +5265,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" s="8" customFormat="1" spans="1:2">
@@ -5262,7 +5273,7 @@
         <v>29</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" s="8" customFormat="1" spans="1:2">
@@ -5270,7 +5281,7 @@
         <v>31</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" s="8" customFormat="1" spans="1:2">
@@ -5278,7 +5289,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" s="8" customFormat="1" spans="1:2">
@@ -5286,7 +5297,7 @@
         <v>37</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" s="8" customFormat="1" spans="1:2">
@@ -5294,7 +5305,7 @@
         <v>43</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" s="8" customFormat="1" spans="1:2">
@@ -5302,7 +5313,7 @@
         <v>45</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" s="8" customFormat="1" spans="1:2">
@@ -5310,7 +5321,7 @@
         <v>47</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" s="8" customFormat="1" spans="1:2">
@@ -5318,7 +5329,7 @@
         <v>49</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" s="8" customFormat="1" spans="1:2">
@@ -5326,7 +5337,7 @@
         <v>51</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" s="8" customFormat="1" spans="1:2">
@@ -5334,7 +5345,7 @@
         <v>53</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" s="8" customFormat="1" spans="1:2">
@@ -5342,7 +5353,7 @@
         <v>57</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" s="8" customFormat="1" spans="1:2">
@@ -5350,7 +5361,7 @@
         <v>59</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" s="8" customFormat="1" spans="1:2">
@@ -5358,7 +5369,7 @@
         <v>63</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" s="8" customFormat="1" spans="1:2">
@@ -5366,7 +5377,7 @@
         <v>67</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" s="8" customFormat="1" spans="1:2">
@@ -5374,7 +5385,7 @@
         <v>69</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" s="8" customFormat="1" spans="1:2">
@@ -5382,7 +5393,7 @@
         <v>71</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" s="8" customFormat="1" spans="1:2">
@@ -5390,7 +5401,7 @@
         <v>73</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" s="8" customFormat="1" spans="1:2">
@@ -5398,7 +5409,7 @@
         <v>75</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" s="8" customFormat="1" spans="1:2">
@@ -5406,7 +5417,7 @@
         <v>77</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" s="8" customFormat="1" spans="1:2">
@@ -5414,7 +5425,7 @@
         <v>79</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" s="8" customFormat="1" spans="1:2">
@@ -5422,7 +5433,7 @@
         <v>83</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" s="8" customFormat="1" spans="1:2">
@@ -5430,7 +5441,7 @@
         <v>85</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" s="8" customFormat="1" spans="1:2">
@@ -5438,7 +5449,7 @@
         <v>89</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" s="8" customFormat="1" spans="1:2">
@@ -5446,7 +5457,7 @@
         <v>91</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31" s="8" customFormat="1" spans="1:2">
@@ -5454,7 +5465,7 @@
         <v>99</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32" s="8" customFormat="1" spans="1:2">
@@ -5462,7 +5473,7 @@
         <v>105</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="33" s="8" customFormat="1" spans="1:2">
@@ -5470,7 +5481,7 @@
         <v>107</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="34" s="8" customFormat="1" spans="1:2">
@@ -5478,7 +5489,7 @@
         <v>111</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="35" s="8" customFormat="1" spans="1:2">
@@ -5486,7 +5497,7 @@
         <v>113</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="36" s="8" customFormat="1" spans="1:2">
@@ -5494,7 +5505,7 @@
         <v>115</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" s="8" customFormat="1" spans="1:2">
@@ -5502,7 +5513,7 @@
         <v>117</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="38" s="8" customFormat="1" spans="1:2">
@@ -5510,7 +5521,7 @@
         <v>119</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39" s="8" customFormat="1" spans="1:2">
@@ -5518,7 +5529,7 @@
         <v>121</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="40" s="8" customFormat="1" spans="1:2">
@@ -5526,7 +5537,7 @@
         <v>125</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="41" s="8" customFormat="1" spans="1:2">
@@ -5534,7 +5545,7 @@
         <v>127</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42" s="8" customFormat="1" spans="1:2">
@@ -5542,7 +5553,7 @@
         <v>139</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="43" s="8" customFormat="1" spans="1:2">
@@ -5550,7 +5561,7 @@
         <v>141</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="44" s="8" customFormat="1" spans="1:2">
@@ -5558,7 +5569,7 @@
         <v>147</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="45" s="8" customFormat="1" spans="1:2">
@@ -5566,7 +5577,7 @@
         <v>153</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" s="8" customFormat="1" spans="1:2">
@@ -5574,7 +5585,7 @@
         <v>155</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="47" s="8" customFormat="1" spans="1:2">
@@ -5582,7 +5593,7 @@
         <v>159</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="48" s="8" customFormat="1" spans="1:2">
@@ -5590,7 +5601,7 @@
         <v>166</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="49" s="8" customFormat="1" spans="1:2">
@@ -5598,7 +5609,7 @@
         <v>170</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="50" s="8" customFormat="1" spans="1:2">
@@ -5606,7 +5617,7 @@
         <v>171</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51" s="8" customFormat="1" spans="1:2">
@@ -5614,7 +5625,7 @@
         <v>173</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="52" s="8" customFormat="1" spans="1:2">
@@ -5622,7 +5633,7 @@
         <v>175</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53" s="8" customFormat="1" spans="1:2">
@@ -5630,7 +5641,7 @@
         <v>179</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="54" s="8" customFormat="1" spans="1:2">
@@ -5638,7 +5649,7 @@
         <v>185</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="55" s="8" customFormat="1" spans="1:2">
@@ -5646,7 +5657,7 @@
         <v>187</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="56" s="8" customFormat="1" spans="1:2">
@@ -5654,7 +5665,7 @@
         <v>193</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="57" s="8" customFormat="1" spans="1:2">
@@ -5662,7 +5673,7 @@
         <v>195</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="58" s="8" customFormat="1" spans="1:2">
@@ -5670,7 +5681,7 @@
         <v>199</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="59" s="8" customFormat="1" spans="1:2">
@@ -5678,7 +5689,7 @@
         <v>203</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="60" s="8" customFormat="1" spans="1:2">
@@ -5686,7 +5697,7 @@
         <v>213</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="61" s="8" customFormat="1" spans="1:2">
@@ -5694,7 +5705,7 @@
         <v>215</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="62" s="8" customFormat="1" spans="1:2">
@@ -5702,7 +5713,7 @@
         <v>217</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="63" s="8" customFormat="1" spans="1:2">
@@ -5710,7 +5721,7 @@
         <v>221</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="64" s="8" customFormat="1" spans="1:2">
@@ -5718,7 +5729,7 @@
         <v>223</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="65" s="8" customFormat="1" spans="1:2">
@@ -5726,7 +5737,7 @@
         <v>228</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="66" s="8" customFormat="1" spans="1:2">
@@ -5734,7 +5745,7 @@
         <v>231</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="67" s="8" customFormat="1" spans="1:2">
@@ -5742,7 +5753,7 @@
         <v>237</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68" s="8" customFormat="1" spans="1:2">
@@ -5750,7 +5761,7 @@
         <v>245</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="69" s="8" customFormat="1" spans="1:2">
@@ -5758,7 +5769,7 @@
         <v>251</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="70" s="8" customFormat="1" spans="1:2">
@@ -5766,7 +5777,7 @@
         <v>261</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="71" s="8" customFormat="1" spans="1:2">
@@ -5774,7 +5785,7 @@
         <v>267</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="72" s="8" customFormat="1" spans="1:2">
@@ -5782,7 +5793,7 @@
         <v>275</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="73" s="8" customFormat="1" spans="1:2">
@@ -5790,7 +5801,7 @@
         <v>287</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="74" s="8" customFormat="1" spans="1:2">
@@ -5798,7 +5809,7 @@
         <v>309</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="75" s="8" customFormat="1" spans="1:2">
@@ -5806,7 +5817,7 @@
         <v>311</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="76" s="8" customFormat="1" spans="1:2">
@@ -5814,7 +5825,7 @@
         <v>315</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="77" s="8" customFormat="1" spans="1:2">
@@ -5822,7 +5833,7 @@
         <v>319</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="78" s="8" customFormat="1" spans="1:2">
@@ -5830,7 +5841,7 @@
         <v>323</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="79" s="8" customFormat="1" spans="1:2">
@@ -5838,7 +5849,7 @@
         <v>349</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="80" s="8" customFormat="1" spans="1:2">
@@ -5846,7 +5857,7 @@
         <v>353</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="81" s="8" customFormat="1" spans="1:2">
@@ -5854,7 +5865,7 @@
         <v>365</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="82" s="8" customFormat="1" spans="1:2">
@@ -5862,7 +5873,7 @@
         <v>393</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="83" s="8" customFormat="1" spans="1:2">
@@ -5870,7 +5881,7 @@
         <v>399</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="84" s="8" customFormat="1" spans="1:2">
@@ -5878,7 +5889,7 @@
         <v>421</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="85" s="8" customFormat="1" spans="1:2">
@@ -5886,7 +5897,7 @@
         <v>477</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="86" s="8" customFormat="1" spans="1:2">
@@ -5894,7 +5905,7 @@
         <v>491</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="87" s="8" customFormat="1" spans="1:2">
@@ -5902,7 +5913,7 @@
         <v>497</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="88" s="8" customFormat="1" spans="1:2">
@@ -5910,7 +5921,7 @@
         <v>499</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="89" s="8" customFormat="1" spans="1:2">
@@ -5918,7 +5929,7 @@
         <v>511</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" s="8" customFormat="1" spans="1:2">
@@ -5926,7 +5937,7 @@
         <v>513</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="91" s="8" customFormat="1" spans="1:2">
@@ -5934,7 +5945,7 @@
         <v>519</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" s="8" customFormat="1" spans="1:2">
@@ -5942,7 +5953,7 @@
         <v>535</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="93" s="8" customFormat="1" spans="1:2">
@@ -5950,7 +5961,7 @@
         <v>559</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="94" s="8" customFormat="1" spans="1:2">
@@ -5958,7 +5969,7 @@
         <v>561</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="95" s="8" customFormat="1" spans="1:2">
@@ -5966,7 +5977,7 @@
         <v>587</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="96" s="8" customFormat="1" spans="1:2">
@@ -5974,7 +5985,7 @@
         <v>605</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="97" s="8" customFormat="1" spans="1:2">
@@ -5982,7 +5993,7 @@
         <v>709</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="98" s="8" customFormat="1" spans="1:2">
@@ -5990,7 +6001,7 @@
         <v>751</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="99" s="8" customFormat="1" spans="1:2">
@@ -5998,7 +6009,7 @@
         <v>845</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="100" s="8" customFormat="1" spans="1:2">
@@ -6006,7 +6017,7 @@
         <v>875</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="101" s="8" customFormat="1" spans="1:2">
@@ -6014,7 +6025,7 @@
         <v>887</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="102" s="8" customFormat="1" spans="1:2">
@@ -6022,7 +6033,7 @@
         <v>907</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="103" s="8" customFormat="1" spans="1:2">
@@ -6030,7 +6041,7 @@
         <v>919</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="104" s="8" customFormat="1" spans="1:2">
@@ -6038,7 +6049,7 @@
         <v>951</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="105" s="8" customFormat="1" spans="1:2">
@@ -6046,7 +6057,7 @@
         <v>959</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="106" s="8" customFormat="1" spans="1:2">
@@ -6054,7 +6065,7 @@
         <v>961</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="107" s="8" customFormat="1" spans="1:2">
@@ -6062,7 +6073,7 @@
         <v>1491</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="108" s="8" customFormat="1" spans="1:2">
@@ -6070,7 +6081,7 @@
         <v>1501</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="109" s="8" customFormat="1" spans="1:2">
@@ -6078,7 +6089,7 @@
         <v>1533</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="110" s="8" customFormat="1" spans="1:2">
@@ -6086,7 +6097,7 @@
         <v>1543</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="111" s="8" customFormat="1" spans="1:2">
@@ -6094,7 +6105,7 @@
         <v>1545</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="112" s="8" customFormat="1" spans="1:2">
@@ -6102,7 +6113,7 @@
         <v>1572</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="113" s="8" customFormat="1" spans="1:2">
@@ -6110,7 +6121,7 @@
         <v>1595</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="114" s="8" customFormat="1" spans="1:2">
@@ -6118,7 +6129,7 @@
         <v>1596</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="115" s="8" customFormat="1" spans="1:2">
@@ -6126,7 +6137,7 @@
         <v>1598</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="116" s="8" customFormat="1" spans="1:2">
@@ -6134,7 +6145,7 @@
         <v>1600</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="117" s="8" customFormat="1" spans="1:2">
@@ -6142,7 +6153,7 @@
         <v>1608</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="118" s="8" customFormat="1" spans="1:2">
@@ -6150,7 +6161,7 @@
         <v>1611</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="119" s="8" customFormat="1" spans="1:2">
@@ -6158,7 +6169,7 @@
         <v>1620</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="120" s="8" customFormat="1" spans="1:2">
@@ -6166,7 +6177,7 @@
         <v>1634</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="121" s="8" customFormat="1" spans="1:2">
@@ -6174,7 +6185,7 @@
         <v>1636</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="122" s="8" customFormat="1" spans="1:2">
@@ -6182,7 +6193,7 @@
         <v>1647</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="123" s="8" customFormat="1" spans="1:2">
@@ -6190,7 +6201,7 @@
         <v>1648</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="124" s="8" customFormat="1" spans="1:2">
@@ -6198,7 +6209,7 @@
         <v>1649</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="125" s="8" customFormat="1" spans="1:2">
@@ -6206,7 +6217,7 @@
         <v>1670</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="126" s="8" customFormat="1" spans="1:2">
@@ -6214,7 +6225,7 @@
         <v>1704</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="127" s="8" customFormat="1" spans="1:2">
@@ -6222,7 +6233,7 @@
         <v>1705</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="128" s="8" customFormat="1" spans="1:2">
@@ -6230,7 +6241,7 @@
         <v>1706</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="129" s="8" customFormat="1" spans="1:2">
@@ -6238,7 +6249,7 @@
         <v>1707</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="130" s="8" customFormat="1" spans="1:2">
@@ -6246,7 +6257,7 @@
         <v>1755</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="131" s="8" customFormat="1" spans="1:2">
@@ -6254,7 +6265,7 @@
         <v>1757</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="132" s="8" customFormat="1" spans="1:2">
@@ -6262,7 +6273,7 @@
         <v>1827</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="133" s="8" customFormat="1" spans="1:2">
@@ -6270,7 +6281,7 @@
         <v>1851</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="134" s="8" customFormat="1" spans="1:2">
@@ -6278,7 +6289,7 @@
         <v>1855</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="135" s="8" customFormat="1" spans="1:2">
@@ -6286,7 +6297,7 @@
         <v>1856</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="136" s="8" customFormat="1" spans="1:2">
@@ -6294,7 +6305,7 @@
         <v>1906</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="137" s="8" customFormat="1" spans="1:2">
@@ -6302,7 +6313,7 @@
         <v>1985</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="138" s="8" customFormat="1" spans="1:2">
@@ -6310,7 +6321,7 @@
         <v>1986</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="139" s="8" customFormat="1" spans="1:2">
@@ -6318,7 +6329,7 @@
         <v>2051</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="140" s="8" customFormat="1" spans="1:2">
@@ -6326,7 +6337,7 @@
         <v>2091</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="141" s="8" customFormat="1" spans="1:2">
@@ -6334,7 +6345,7 @@
         <v>2196</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="142" s="8" customFormat="1" spans="1:2">
@@ -6342,7 +6353,7 @@
         <v>2197</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="143" s="8" customFormat="1" spans="1:2">
@@ -6350,7 +6361,7 @@
         <v>2212</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="144" s="8" customFormat="1" spans="1:2">
@@ -6358,7 +6369,7 @@
         <v>2285</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="145" s="8" customFormat="1" spans="1:2">
@@ -6366,7 +6377,7 @@
         <v>2286</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="146" s="8" customFormat="1" spans="1:2">
@@ -6374,7 +6385,7 @@
         <v>2361</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="147" s="8" customFormat="1" spans="1:2">
@@ -6382,7 +6393,7 @@
         <v>2525</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="148" s="8" customFormat="1" spans="1:2">
@@ -6390,7 +6401,7 @@
         <v>2627</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="149" s="8" customFormat="1" spans="1:2">
@@ -6398,7 +6409,7 @@
         <v>2720</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="150" s="8" customFormat="1" spans="1:2">
@@ -6406,7 +6417,7 @@
         <v>2735</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="151" s="8" customFormat="1" spans="1:2">
@@ -6414,7 +6425,7 @@
         <v>2768</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="152" s="8" customFormat="1" spans="1:2">
@@ -6422,7 +6433,7 @@
         <v>2769</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="153" s="8" customFormat="1" spans="1:2">
@@ -6430,7 +6441,7 @@
         <v>2770</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="154" s="8" customFormat="1" spans="1:2">
@@ -6438,7 +6449,7 @@
         <v>3194</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="155" s="8" customFormat="1" spans="1:2">
@@ -6446,7 +6457,7 @@
         <v>3208</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="156" s="8" customFormat="1" spans="1:2">
@@ -6454,7 +6465,7 @@
         <v>3320</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="157" s="8" customFormat="1" spans="1:2">
@@ -6462,7 +6473,7 @@
         <v>3328</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="158" s="8" customFormat="1" spans="1:2">
@@ -6470,7 +6481,7 @@
         <v>3340</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="159" s="8" customFormat="1" spans="1:2">
@@ -6478,7 +6489,7 @@
         <v>3342</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="160" s="8" customFormat="1" spans="1:2">
@@ -6486,7 +6497,7 @@
         <v>3344</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="161" s="8" customFormat="1" spans="1:2">
@@ -6494,7 +6505,7 @@
         <v>3393</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="162" s="8" customFormat="1" spans="1:2">
@@ -6502,7 +6513,7 @@
         <v>3394</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="163" s="8" customFormat="1" spans="1:2">
@@ -6510,7 +6521,7 @@
         <v>3395</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="164" s="8" customFormat="1" spans="1:2">
@@ -6518,7 +6529,7 @@
         <v>3446</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="165" s="8" customFormat="1" spans="1:2">
@@ -6526,7 +6537,7 @@
         <v>3549</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="166" s="8" customFormat="1" spans="1:2">
@@ -6534,7 +6545,7 @@
         <v>3662</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="167" s="8" customFormat="1" spans="1:2">
@@ -6542,7 +6553,7 @@
         <v>3755</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="168" s="8" customFormat="1" spans="1:2">
@@ -6550,7 +6561,7 @@
         <v>3756</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="169" s="8" customFormat="1" spans="1:2">
@@ -6558,7 +6569,7 @@
         <v>3854</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="170" s="8" customFormat="1" spans="1:2">
@@ -6566,7 +6577,7 @@
         <v>3858</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="171" s="8" customFormat="1" spans="1:2">
@@ -6574,7 +6585,7 @@
         <v>3873</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="172" s="8" customFormat="1" spans="1:2">
@@ -6582,7 +6593,7 @@
         <v>3951</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="173" s="8" customFormat="1" spans="1:2">
@@ -6590,7 +6601,7 @@
         <v>4024</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="174" s="8" customFormat="1" spans="1:2">
@@ -6598,7 +6609,7 @@
         <v>4054</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="175" s="8" customFormat="1" spans="1:2">
@@ -6606,7 +6617,7 @@
         <v>4132</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="176" s="8" customFormat="1" spans="1:2">
@@ -6614,7 +6625,7 @@
         <v>4133</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="177" s="8" customFormat="1" spans="1:2">
@@ -6622,7 +6633,7 @@
         <v>4154</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="178" s="8" customFormat="1" spans="1:2">
@@ -6630,7 +6641,7 @@
         <v>4224</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="179" s="8" customFormat="1" spans="1:2">
@@ -6638,7 +6649,7 @@
         <v>4228</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="180" s="8" customFormat="1" spans="1:2">
@@ -6646,7 +6657,7 @@
         <v>4259</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="181" s="8" customFormat="1" spans="1:2">
@@ -6654,7 +6665,7 @@
         <v>4272</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="182" s="8" customFormat="1" spans="1:2">
@@ -6662,7 +6673,7 @@
         <v>4289</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="183" s="8" customFormat="1" spans="1:2">
@@ -6670,7 +6681,7 @@
         <v>4290</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="184" s="8" customFormat="1" spans="1:2">
@@ -6678,7 +6689,7 @@
         <v>4291</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="185" s="8" customFormat="1" spans="1:2">
@@ -6686,7 +6697,7 @@
         <v>4292</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="186" s="8" customFormat="1" spans="1:2">
@@ -6694,7 +6705,7 @@
         <v>4293</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="187" s="8" customFormat="1" spans="1:2">
@@ -6702,7 +6713,7 @@
         <v>4294</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="188" s="8" customFormat="1" spans="1:2">
@@ -6710,7 +6721,7 @@
         <v>4295</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="189" s="8" customFormat="1" spans="1:2">
@@ -6718,7 +6729,7 @@
         <v>4296</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="190" s="8" customFormat="1" spans="1:2">
@@ -6726,7 +6737,7 @@
         <v>4297</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="191" s="8" customFormat="1" spans="1:2">
@@ -6734,7 +6745,7 @@
         <v>4298</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="192" s="8" customFormat="1" spans="1:2">
@@ -6742,7 +6753,7 @@
         <v>4299</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="193" s="8" customFormat="1" spans="1:2">
@@ -6750,7 +6761,7 @@
         <v>4300</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="194" s="8" customFormat="1" spans="1:2">
@@ -6758,7 +6769,7 @@
         <v>4301</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="195" s="8" customFormat="1" spans="1:2">
@@ -6766,7 +6777,7 @@
         <v>4302</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="196" s="8" customFormat="1" spans="1:2">
@@ -6774,7 +6785,7 @@
         <v>4303</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="197" s="8" customFormat="1" spans="1:2">
@@ -6782,7 +6793,7 @@
         <v>4304</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="198" s="8" customFormat="1" spans="1:2">
@@ -6790,7 +6801,7 @@
         <v>4305</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="199" s="8" customFormat="1" spans="1:2">
@@ -6798,7 +6809,7 @@
         <v>4306</v>
       </c>
       <c r="B199" s="8" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="200" s="8" customFormat="1" spans="1:2">
@@ -6806,7 +6817,7 @@
         <v>4307</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="201" s="8" customFormat="1" spans="1:2">
@@ -6814,7 +6825,7 @@
         <v>4308</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="202" s="8" customFormat="1" spans="1:2">
@@ -6822,7 +6833,7 @@
         <v>4309</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="203" s="8" customFormat="1" spans="1:2">
@@ -6830,7 +6841,7 @@
         <v>4311</v>
       </c>
       <c r="B203" s="8" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="204" s="8" customFormat="1" spans="1:2">
@@ -6838,7 +6849,7 @@
         <v>4312</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="205" s="8" customFormat="1" spans="1:2">
@@ -6846,7 +6857,7 @@
         <v>4313</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="206" s="8" customFormat="1" spans="1:2">
@@ -6854,7 +6865,7 @@
         <v>4314</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="207" s="8" customFormat="1" spans="1:2">
@@ -6862,7 +6873,7 @@
         <v>4315</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="208" s="8" customFormat="1" spans="1:2">
@@ -6870,7 +6881,7 @@
         <v>4316</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="209" s="8" customFormat="1" spans="1:2">
@@ -6878,7 +6889,7 @@
         <v>4317</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="210" s="8" customFormat="1" spans="1:2">
@@ -6886,7 +6897,7 @@
         <v>4319</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="211" s="8" customFormat="1" spans="1:2">
@@ -6894,7 +6905,7 @@
         <v>4320</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="212" s="8" customFormat="1" spans="1:2">
@@ -6902,7 +6913,7 @@
         <v>4321</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="213" s="8" customFormat="1" spans="1:2">
@@ -6910,7 +6921,7 @@
         <v>4329</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="214" s="8" customFormat="1" spans="1:2">
@@ -6918,7 +6929,7 @@
         <v>4330</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="215" s="8" customFormat="1" spans="1:2">
@@ -6926,7 +6937,7 @@
         <v>4331</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="216" s="8" customFormat="1" spans="1:2">
@@ -6934,7 +6945,7 @@
         <v>4332</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="217" s="8" customFormat="1" spans="1:2">
@@ -6942,7 +6953,7 @@
         <v>4333</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="218" s="8" customFormat="1" spans="1:2">
@@ -6950,7 +6961,7 @@
         <v>4334</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="219" s="8" customFormat="1" spans="1:2">
@@ -6958,7 +6969,7 @@
         <v>4335</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="220" s="8" customFormat="1" spans="1:2">
@@ -6966,7 +6977,7 @@
         <v>4336</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="221" s="8" customFormat="1" spans="1:2">
@@ -6974,7 +6985,7 @@
         <v>4337</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="222" s="8" customFormat="1" spans="1:2">
@@ -6982,7 +6993,7 @@
         <v>4338</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="223" s="8" customFormat="1" spans="1:2">
@@ -6990,7 +7001,7 @@
         <v>4339</v>
       </c>
       <c r="B223" s="8" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="224" s="8" customFormat="1" spans="1:2">
@@ -6998,7 +7009,7 @@
         <v>4346</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="225" s="8" customFormat="1" spans="1:2">
@@ -7006,7 +7017,7 @@
         <v>4347</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="226" s="8" customFormat="1" spans="1:2">
@@ -7014,7 +7025,7 @@
         <v>4348</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="227" s="8" customFormat="1" spans="1:2">
@@ -7022,7 +7033,7 @@
         <v>4349</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="228" s="8" customFormat="1" spans="1:2">
@@ -7030,7 +7041,7 @@
         <v>4350</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="229" s="8" customFormat="1" spans="1:2">
@@ -7038,7 +7049,7 @@
         <v>4351</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="230" s="8" customFormat="1" spans="1:2">
@@ -7046,7 +7057,7 @@
         <v>4352</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="231" s="8" customFormat="1" spans="1:2">
@@ -7054,7 +7065,7 @@
         <v>4412</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="232" s="8" customFormat="1" spans="1:2">
@@ -7062,7 +7073,7 @@
         <v>4413</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="233" s="8" customFormat="1" spans="1:2">
@@ -7070,7 +7081,7 @@
         <v>4414</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="234" s="8" customFormat="1" spans="1:2">
@@ -7078,7 +7089,7 @@
         <v>4419</v>
       </c>
       <c r="B234" s="8" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="235" s="8" customFormat="1" spans="1:2">
@@ -7086,7 +7097,7 @@
         <v>4422</v>
       </c>
       <c r="B235" s="8" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="236" s="8" customFormat="1" spans="1:2">
@@ -7094,7 +7105,7 @@
         <v>4425</v>
       </c>
       <c r="B236" s="8" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="237" s="8" customFormat="1" spans="1:2">
@@ -7102,7 +7113,7 @@
         <v>4452</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="238" s="8" customFormat="1" spans="1:2">
@@ -7110,7 +7121,7 @@
         <v>4453</v>
       </c>
       <c r="B238" s="8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="239" s="8" customFormat="1" spans="1:2">
@@ -7118,7 +7129,7 @@
         <v>4454</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="240" s="8" customFormat="1" spans="1:2">
@@ -7126,7 +7137,7 @@
         <v>4455</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="241" s="8" customFormat="1" spans="1:2">
@@ -7134,7 +7145,7 @@
         <v>4456</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="242" s="8" customFormat="1" spans="1:2">
@@ -7142,7 +7153,7 @@
         <v>4457</v>
       </c>
       <c r="B242" s="8" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="243" s="8" customFormat="1" spans="1:2">
@@ -7150,7 +7161,7 @@
         <v>4458</v>
       </c>
       <c r="B243" s="8" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="244" s="8" customFormat="1" spans="1:2">
@@ -7158,7 +7169,7 @@
         <v>4459</v>
       </c>
       <c r="B244" s="8" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="245" s="8" customFormat="1" spans="1:2">
@@ -7166,7 +7177,7 @@
         <v>4479</v>
       </c>
       <c r="B245" s="8" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="246" s="8" customFormat="1" spans="1:2">
@@ -7174,7 +7185,7 @@
         <v>4509</v>
       </c>
       <c r="B246" s="8" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="247" s="8" customFormat="1" spans="1:2">
@@ -7182,7 +7193,7 @@
         <v>4514</v>
       </c>
       <c r="B247" s="8" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="248" s="8" customFormat="1" spans="1:2">
@@ -7190,7 +7201,7 @@
         <v>4536</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -7205,6 +7216,7 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
+    <col min="1" max="1" width="19.6057692307692" customWidth="1"/>
     <col min="2" max="2" width="16.9807692307692" customWidth="1"/>
     <col min="3" max="3" width="28.2019230769231" customWidth="1"/>
     <col min="4" max="4" width="51.2692307692308" customWidth="1"/>
@@ -7212,65 +7224,65 @@
   <sheetData>
     <row r="1" ht="232" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:5">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>546</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="3" ht="146" customHeight="1" spans="1:5">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="4" ht="51" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="6" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3"/>

--- a/基础数据.xlsx
+++ b/基础数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18460" activeTab="4"/>
+    <workbookView windowWidth="25600" windowHeight="8960"/>
   </bookViews>
   <sheets>
     <sheet name="唯普库" sheetId="1" r:id="rId1"/>
